--- a/experiment_results/wedos_grid/rtt_bursts_S1_atk1pct_wu500000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S1_atk1pct_wu500000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
